--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -953,9 +953,8 @@
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +214,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,327 +628,246 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Indigenous – Chancellery Indigenous</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 6a, so please include any relevant activity from across 2026.
 Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="I16" s="14" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1008,7 +907,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1020,12 +919,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1033,77 +932,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1154,93 +1053,93 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Chancellery Indigenous</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Case studies demonstrating the two-way learning and increased understanding with topics and methods to be developed as part of cocreation or Indigenous-led activity</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr"/>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -1263,13 +1162,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1285,21 +1184,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1208,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1357,24 +1225,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1390,47 +1242,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -1438,11 +1258,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,201 +641,204 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Indigenous – Chancellery Indigenous</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="171" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 6a, so please include any relevant activity from across 2026.
 Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
@@ -899,110 +882,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1033,113 +1008,102 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chancellery Indigenous</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Chancellery Indigenous</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Case studies demonstrating the two-way learning and increased understanding with topics and methods to be developed as part of cocreation or Indigenous-led activity</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr"/>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -1162,10 +1126,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1187,7 +1158,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1209,7 +1180,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1226,7 +1197,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1243,35 +1214,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Indigenous – Chancellery Indigenous</t>
         </is>
@@ -652,193 +787,193 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="171" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>We did not receive an end-2025 response for the related SP2030 target 6a, so please include any relevant activity from across 2026.
-Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.
+We did not receive an end-2025 response for the related SP2030 target 6a, so please include any relevant activity from across 2026.</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
@@ -858,6 +993,7 @@
     <hyperlink ref="H16" location="'3. SR25 responses'!B7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -867,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -880,104 +1016,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -985,6 +1165,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -994,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1006,104 +1187,149 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chancellery Indigenous</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Chancellery Indigenous</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Case studies demonstrating the two-way learning and increased understanding with topics and methods to be developed as part of cocreation or Indigenous-led activity</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -1117,6 +1343,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Indigenous - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -950,7 +931,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples or case studies from your Faculty/Portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.
+          <t>Please provide examples or case studies from your portfolio of sustainability outcomes informed by Indigenous knowledges. Describe the activity or decision, how Indigenous knowledges were incorporated or co-created, who was involved, and the resulting sustainability outcome.
 We did not receive an end-2025 response for the related SP2030 target 6a, so please include any relevant activity from across 2026.</t>
         </is>
       </c>
@@ -972,23 +953,16 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B7"/>
   </hyperlinks>
